--- a/diseases/d128/2000-2004.xlsx
+++ b/diseases/d128/2000-2004.xlsx
@@ -55847,17 +55847,17 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>DE-NI</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Niedersachsen, Germany</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -55896,33 +55896,134 @@
       <c r="O409" t="n">
         <v>1</v>
       </c>
+      <c r="P409" t="n">
+        <v>1</v>
+      </c>
       <c r="U409" t="inlineStr">
         <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="V409" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="W409" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X409" t="inlineStr">
+        <is>
+          <t>__source_native__</t>
+        </is>
+      </c>
+      <c r="Y409" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z409" t="inlineStr">
+        <is>
+          <t>national_ifsG_notification_registry</t>
+        </is>
+      </c>
+      <c r="AA409" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB409" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC409" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD409" t="inlineStr">
+        <is>
+          <t>sha256:ffcb24f78ecc3d9ae732caf86a9d5bdb915c979773cdb4a208a655097464cc61</t>
+        </is>
+      </c>
+      <c r="AE409" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF409" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG409" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH409" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI409" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ409" t="inlineStr">
+        <is>
+          <t>DE_RKI_SURVSTAT_source_native</t>
+        </is>
+      </c>
+      <c r="AK409" t="inlineStr">
+        <is>
+          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
+        </is>
+      </c>
+      <c r="AM409" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN409" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO409" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP409" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ409" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR409" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS409" t="inlineStr">
+        <is>
           <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
         </is>
       </c>
-      <c r="AA409" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO409" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP409" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS409" t="inlineStr">
-        <is>
-          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
-        </is>
-      </c>
       <c r="AT409" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="AU409" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV409" t="inlineStr">
         <is>
@@ -55936,12 +56037,12 @@
       </c>
       <c r="AX409" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY409" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ409" t="inlineStr">
@@ -55956,12 +56057,12 @@
       </c>
       <c r="BB409" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC409" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -55993,12 +56094,12 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>DE-BY</t>
+          <t>DE-NI</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Bayern, Germany</t>
+          <t>Niedersachsen, Germany</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -56023,7 +56124,7 @@
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>2003-09-22</t>
+          <t>2003-09-01</t>
         </is>
       </c>
       <c r="M410" t="inlineStr">
@@ -56037,6 +56138,11 @@
       <c r="O410" t="n">
         <v>1</v>
       </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U410" t="inlineStr">
         <is>
           <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
@@ -56054,7 +56160,12 @@
       </c>
       <c r="AP410" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ410" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS410" t="inlineStr">
@@ -56064,6 +56175,11 @@
       </c>
       <c r="AT410" t="n">
         <v>1</v>
+      </c>
+      <c r="AU410" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV410" t="inlineStr">
         <is>
@@ -56129,17 +56245,17 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>DE-NI</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Niedersachsen, Germany</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -56164,12 +56280,12 @@
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2003-09-01</t>
         </is>
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>2003-10</t>
+          <t>2003-09</t>
         </is>
       </c>
       <c r="N411" t="n">
@@ -56178,69 +56294,165 @@
       <c r="O411" t="n">
         <v>1</v>
       </c>
-      <c r="Q411" t="n">
-        <v>0</v>
-      </c>
-      <c r="R411" t="n">
-        <v>0.005045547545216242</v>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
+        </is>
+      </c>
+      <c r="V411" t="inlineStr">
+        <is>
+          <t>west-nil-virus</t>
+        </is>
+      </c>
+      <c r="W411" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X411" t="inlineStr">
+        <is>
+          <t>West-Nil-Virus</t>
+        </is>
+      </c>
+      <c r="Y411" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z411" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
       </c>
       <c r="AA411" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB411" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC411" t="inlineStr">
+        <is>
+          <t>country:DE-NI:national</t>
+        </is>
+      </c>
+      <c r="AD411" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE411" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF411" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG411" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH411" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI411" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ411" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL411" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM411" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN411" t="b">
+        <v>1</v>
       </c>
       <c r="AO411" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP411" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS411" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ411" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS411" t="inlineStr">
+        <is>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
+        </is>
+      </c>
       <c r="AT411" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU411" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV411" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW411" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX411" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY411" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ411" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA411" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB411" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC411" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56267,17 +56479,17 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -56302,80 +56514,187 @@
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2003-09-22</t>
         </is>
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>2003-10</t>
+          <t>2003-09</t>
         </is>
       </c>
       <c r="N412" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O412" t="n">
-        <v>0</v>
-      </c>
-      <c r="R412" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P412" t="n">
+        <v>1</v>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="V412" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="W412" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X412" t="inlineStr">
+        <is>
+          <t>__source_native__</t>
+        </is>
+      </c>
+      <c r="Y412" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z412" t="inlineStr">
+        <is>
+          <t>national_ifsG_notification_registry</t>
+        </is>
       </c>
       <c r="AA412" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB412" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC412" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD412" t="inlineStr">
+        <is>
+          <t>sha256:ffcb24f78ecc3d9ae732caf86a9d5bdb915c979773cdb4a208a655097464cc61</t>
+        </is>
+      </c>
+      <c r="AE412" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF412" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG412" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH412" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI412" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ412" t="inlineStr">
+        <is>
+          <t>DE_RKI_SURVSTAT_source_native</t>
+        </is>
+      </c>
+      <c r="AK412" t="inlineStr">
+        <is>
+          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
+        </is>
+      </c>
+      <c r="AM412" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN412" t="b">
+        <v>0</v>
       </c>
       <c r="AO412" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP412" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS412" t="inlineStr"/>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ412" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR412" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS412" t="inlineStr">
+        <is>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
+        </is>
+      </c>
       <c r="AT412" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="AU412" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV412" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW412" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX412" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY412" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ412" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA412" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB412" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC412" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -56407,12 +56726,12 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>DE-BY</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Bayern, Germany</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -56437,80 +56756,101 @@
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2003-09-22</t>
         </is>
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>2003-10</t>
+          <t>2003-09</t>
         </is>
       </c>
       <c r="N413" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O413" t="n">
-        <v>0</v>
-      </c>
-      <c r="R413" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
+        </is>
       </c>
       <c r="AA413" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO413" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP413" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS413" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ413" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS413" t="inlineStr">
+        <is>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
+        </is>
+      </c>
       <c r="AT413" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU413" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV413" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW413" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX413" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY413" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ413" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA413" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB413" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC413" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56537,17 +56877,17 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>DE-BY</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Bayern, Germany</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -56572,80 +56912,179 @@
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2003-09-22</t>
         </is>
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>2003-10</t>
+          <t>2003-09</t>
         </is>
       </c>
       <c r="N414" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O414" t="n">
-        <v>0</v>
-      </c>
-      <c r="R414" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
+        </is>
+      </c>
+      <c r="V414" t="inlineStr">
+        <is>
+          <t>west-nil-virus</t>
+        </is>
+      </c>
+      <c r="W414" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X414" t="inlineStr">
+        <is>
+          <t>West-Nil-Virus</t>
+        </is>
+      </c>
+      <c r="Y414" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z414" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
       </c>
       <c r="AA414" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB414" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC414" t="inlineStr">
+        <is>
+          <t>country:DE-BY:national</t>
+        </is>
+      </c>
+      <c r="AD414" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE414" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF414" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG414" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH414" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI414" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ414" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL414" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM414" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN414" t="b">
+        <v>1</v>
       </c>
       <c r="AO414" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP414" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS414" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ414" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS414" t="inlineStr">
+        <is>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
+        </is>
+      </c>
       <c r="AT414" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU414" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV414" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW414" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX414" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY414" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ414" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA414" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB414" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC414" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56677,12 +57116,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -56714,6 +57153,18 @@
         <is>
           <t>2003-10</t>
         </is>
+      </c>
+      <c r="N415" t="n">
+        <v>1</v>
+      </c>
+      <c r="O415" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q415" t="n">
+        <v>0</v>
+      </c>
+      <c r="R415" t="n">
+        <v>0.005045547545216242</v>
       </c>
       <c r="AA415" t="inlineStr">
         <is>
@@ -56741,12 +57192,12 @@
       </c>
       <c r="AW415" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX415" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY415" t="inlineStr">
@@ -56761,12 +57212,12 @@
       </c>
       <c r="BA415" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB415" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC415" t="inlineStr">
@@ -56803,12 +57254,12 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -56876,7 +57327,7 @@
       </c>
       <c r="AW416" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX416" t="inlineStr">
@@ -56896,7 +57347,7 @@
       </c>
       <c r="BA416" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB416" t="inlineStr">
@@ -56938,12 +57389,12 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -57011,7 +57462,7 @@
       </c>
       <c r="AW417" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX417" t="inlineStr">
@@ -57031,7 +57482,7 @@
       </c>
       <c r="BA417" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB417" t="inlineStr">
@@ -57073,12 +57524,12 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -57146,7 +57597,7 @@
       </c>
       <c r="AW418" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX418" t="inlineStr">
@@ -57166,7 +57617,7 @@
       </c>
       <c r="BA418" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB418" t="inlineStr">
@@ -57208,12 +57659,12 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -57245,15 +57696,6 @@
         <is>
           <t>2003-10</t>
         </is>
-      </c>
-      <c r="N419" t="n">
-        <v>0</v>
-      </c>
-      <c r="O419" t="n">
-        <v>0</v>
-      </c>
-      <c r="R419" t="n">
-        <v>0</v>
       </c>
       <c r="AA419" t="inlineStr">
         <is>
@@ -57281,7 +57723,7 @@
       </c>
       <c r="AW419" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX419" t="inlineStr">
@@ -57301,7 +57743,7 @@
       </c>
       <c r="BA419" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB419" t="inlineStr">
@@ -57343,12 +57785,12 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -57373,25 +57815,22 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>2003-11</t>
+          <t>2003-10</t>
         </is>
       </c>
       <c r="N420" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O420" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q420" t="n">
         <v>0</v>
       </c>
       <c r="R420" t="n">
-        <v>0.005045547545216242</v>
+        <v>0</v>
       </c>
       <c r="AA420" t="inlineStr">
         <is>
@@ -57419,12 +57858,12 @@
       </c>
       <c r="AW420" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX420" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY420" t="inlineStr">
@@ -57439,12 +57878,12 @@
       </c>
       <c r="BA420" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB420" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC420" t="inlineStr">
@@ -57481,12 +57920,12 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -57511,12 +57950,12 @@
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>2003-11</t>
+          <t>2003-10</t>
         </is>
       </c>
       <c r="N421" t="n">
@@ -57554,7 +57993,7 @@
       </c>
       <c r="AW421" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX421" t="inlineStr">
@@ -57574,7 +58013,7 @@
       </c>
       <c r="BA421" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB421" t="inlineStr">
@@ -57616,12 +58055,12 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -57646,12 +58085,12 @@
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>2003-11</t>
+          <t>2003-10</t>
         </is>
       </c>
       <c r="N422" t="n">
@@ -57689,7 +58128,7 @@
       </c>
       <c r="AW422" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX422" t="inlineStr">
@@ -57709,7 +58148,7 @@
       </c>
       <c r="BA422" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB422" t="inlineStr">
@@ -57751,12 +58190,12 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -57781,12 +58220,12 @@
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>2003-11</t>
+          <t>2003-10</t>
         </is>
       </c>
       <c r="N423" t="n">
@@ -57824,7 +58263,7 @@
       </c>
       <c r="AW423" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX423" t="inlineStr">
@@ -57844,7 +58283,7 @@
       </c>
       <c r="BA423" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB423" t="inlineStr">
@@ -57886,12 +58325,12 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -57923,6 +58362,18 @@
         <is>
           <t>2003-11</t>
         </is>
+      </c>
+      <c r="N424" t="n">
+        <v>1</v>
+      </c>
+      <c r="O424" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q424" t="n">
+        <v>0</v>
+      </c>
+      <c r="R424" t="n">
+        <v>0.005045547545216242</v>
       </c>
       <c r="AA424" t="inlineStr">
         <is>
@@ -57950,12 +58401,12 @@
       </c>
       <c r="AW424" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX424" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY424" t="inlineStr">
@@ -57970,12 +58421,12 @@
       </c>
       <c r="BA424" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB424" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC424" t="inlineStr">
@@ -58012,12 +58463,12 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -58085,7 +58536,7 @@
       </c>
       <c r="AW425" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX425" t="inlineStr">
@@ -58105,7 +58556,7 @@
       </c>
       <c r="BA425" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB425" t="inlineStr">
@@ -58147,12 +58598,12 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -58220,7 +58671,7 @@
       </c>
       <c r="AW426" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX426" t="inlineStr">
@@ -58240,7 +58691,7 @@
       </c>
       <c r="BA426" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB426" t="inlineStr">
@@ -58282,12 +58733,12 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -58355,7 +58806,7 @@
       </c>
       <c r="AW427" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX427" t="inlineStr">
@@ -58375,7 +58826,7 @@
       </c>
       <c r="BA427" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB427" t="inlineStr">
@@ -58417,12 +58868,12 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -58454,15 +58905,6 @@
         <is>
           <t>2003-11</t>
         </is>
-      </c>
-      <c r="N428" t="n">
-        <v>0</v>
-      </c>
-      <c r="O428" t="n">
-        <v>0</v>
-      </c>
-      <c r="R428" t="n">
-        <v>0</v>
       </c>
       <c r="AA428" t="inlineStr">
         <is>
@@ -58490,7 +58932,7 @@
       </c>
       <c r="AW428" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX428" t="inlineStr">
@@ -58510,7 +58952,7 @@
       </c>
       <c r="BA428" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB428" t="inlineStr">
@@ -58552,12 +58994,12 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -58582,21 +59024,18 @@
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>2003-12</t>
+          <t>2003-11</t>
         </is>
       </c>
       <c r="N429" t="n">
         <v>0</v>
       </c>
       <c r="O429" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q429" t="n">
         <v>0</v>
       </c>
       <c r="R429" t="n">
@@ -58628,12 +59067,12 @@
       </c>
       <c r="AW429" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX429" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY429" t="inlineStr">
@@ -58648,12 +59087,12 @@
       </c>
       <c r="BA429" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB429" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC429" t="inlineStr">
@@ -58690,12 +59129,12 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -58720,12 +59159,12 @@
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>2003-12</t>
+          <t>2003-11</t>
         </is>
       </c>
       <c r="N430" t="n">
@@ -58763,7 +59202,7 @@
       </c>
       <c r="AW430" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX430" t="inlineStr">
@@ -58783,7 +59222,7 @@
       </c>
       <c r="BA430" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB430" t="inlineStr">
@@ -58825,12 +59264,12 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -58855,12 +59294,12 @@
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>2003-12</t>
+          <t>2003-11</t>
         </is>
       </c>
       <c r="N431" t="n">
@@ -58898,7 +59337,7 @@
       </c>
       <c r="AW431" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX431" t="inlineStr">
@@ -58918,7 +59357,7 @@
       </c>
       <c r="BA431" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB431" t="inlineStr">
@@ -58960,12 +59399,12 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -58990,12 +59429,12 @@
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>2003-12</t>
+          <t>2003-11</t>
         </is>
       </c>
       <c r="N432" t="n">
@@ -59033,7 +59472,7 @@
       </c>
       <c r="AW432" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX432" t="inlineStr">
@@ -59053,7 +59492,7 @@
       </c>
       <c r="BA432" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB432" t="inlineStr">
@@ -59095,12 +59534,12 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -59137,6 +59576,9 @@
         <v>0</v>
       </c>
       <c r="O433" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q433" t="n">
         <v>0</v>
       </c>
       <c r="R433" t="n">
@@ -59168,12 +59610,12 @@
       </c>
       <c r="AW433" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX433" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY433" t="inlineStr">
@@ -59188,12 +59630,12 @@
       </c>
       <c r="BA433" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB433" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC433" t="inlineStr">
@@ -59230,12 +59672,12 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -59303,7 +59745,7 @@
       </c>
       <c r="AW434" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX434" t="inlineStr">
@@ -59323,7 +59765,7 @@
       </c>
       <c r="BA434" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB434" t="inlineStr">
@@ -59365,12 +59807,12 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -59438,7 +59880,7 @@
       </c>
       <c r="AW435" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX435" t="inlineStr">
@@ -59458,7 +59900,7 @@
       </c>
       <c r="BA435" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB435" t="inlineStr">
@@ -59500,12 +59942,12 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -59573,7 +60015,7 @@
       </c>
       <c r="AW436" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX436" t="inlineStr">
@@ -59593,7 +60035,7 @@
       </c>
       <c r="BA436" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB436" t="inlineStr">
@@ -59635,12 +60077,12 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -59708,7 +60150,7 @@
       </c>
       <c r="AW437" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX437" t="inlineStr">
@@ -59728,7 +60170,7 @@
       </c>
       <c r="BA437" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB437" t="inlineStr">
@@ -59770,12 +60212,12 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -59800,25 +60242,22 @@
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-12-01</t>
         </is>
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-12</t>
         </is>
       </c>
       <c r="N438" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O438" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q438" t="n">
         <v>0</v>
       </c>
       <c r="R438" t="n">
-        <v>0.004988357920866386</v>
+        <v>0</v>
       </c>
       <c r="AA438" t="inlineStr">
         <is>
@@ -59846,12 +60285,12 @@
       </c>
       <c r="AW438" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX438" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY438" t="inlineStr">
@@ -59866,12 +60305,12 @@
       </c>
       <c r="BA438" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB438" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC438" t="inlineStr">
@@ -59908,12 +60347,12 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -59938,12 +60377,12 @@
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-12-01</t>
         </is>
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-12</t>
         </is>
       </c>
       <c r="N439" t="n">
@@ -59981,7 +60420,7 @@
       </c>
       <c r="AW439" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX439" t="inlineStr">
@@ -60001,7 +60440,7 @@
       </c>
       <c r="BA439" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB439" t="inlineStr">
@@ -60043,12 +60482,12 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -60073,12 +60512,12 @@
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-12-01</t>
         </is>
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-12</t>
         </is>
       </c>
       <c r="N440" t="n">
@@ -60116,7 +60555,7 @@
       </c>
       <c r="AW440" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX440" t="inlineStr">
@@ -60136,7 +60575,7 @@
       </c>
       <c r="BA440" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB440" t="inlineStr">
@@ -60178,12 +60617,12 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -60208,12 +60647,12 @@
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-12-01</t>
         </is>
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-12</t>
         </is>
       </c>
       <c r="N441" t="n">
@@ -60251,7 +60690,7 @@
       </c>
       <c r="AW441" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX441" t="inlineStr">
@@ -60271,7 +60710,7 @@
       </c>
       <c r="BA441" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB441" t="inlineStr">
@@ -60313,12 +60752,12 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -60350,6 +60789,18 @@
         <is>
           <t>2004-01</t>
         </is>
+      </c>
+      <c r="N442" t="n">
+        <v>1</v>
+      </c>
+      <c r="O442" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>0</v>
+      </c>
+      <c r="R442" t="n">
+        <v>0.004988357920866386</v>
       </c>
       <c r="AA442" t="inlineStr">
         <is>
@@ -60377,12 +60828,12 @@
       </c>
       <c r="AW442" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX442" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY442" t="inlineStr">
@@ -60397,12 +60848,12 @@
       </c>
       <c r="BA442" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB442" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC442" t="inlineStr">
@@ -60439,12 +60890,12 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -60512,7 +60963,7 @@
       </c>
       <c r="AW443" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX443" t="inlineStr">
@@ -60532,7 +60983,7 @@
       </c>
       <c r="BA443" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB443" t="inlineStr">
@@ -60574,12 +61025,12 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -60647,7 +61098,7 @@
       </c>
       <c r="AW444" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX444" t="inlineStr">
@@ -60667,7 +61118,7 @@
       </c>
       <c r="BA444" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB444" t="inlineStr">
@@ -60709,12 +61160,12 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -60782,7 +61233,7 @@
       </c>
       <c r="AW445" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX445" t="inlineStr">
@@ -60802,7 +61253,7 @@
       </c>
       <c r="BA445" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB445" t="inlineStr">
@@ -60844,12 +61295,12 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -60881,15 +61332,6 @@
         <is>
           <t>2004-01</t>
         </is>
-      </c>
-      <c r="N446" t="n">
-        <v>0</v>
-      </c>
-      <c r="O446" t="n">
-        <v>0</v>
-      </c>
-      <c r="R446" t="n">
-        <v>0</v>
       </c>
       <c r="AA446" t="inlineStr">
         <is>
@@ -60917,7 +61359,7 @@
       </c>
       <c r="AW446" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX446" t="inlineStr">
@@ -60937,7 +61379,7 @@
       </c>
       <c r="BA446" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB446" t="inlineStr">
@@ -60979,12 +61421,12 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -61018,56 +61460,32 @@
         </is>
       </c>
       <c r="N447" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O447" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="R447" t="n">
-        <v>0.09958709478847508</v>
-      </c>
-      <c r="S447" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U447" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D196_ANNUAL</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AA447" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO447" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP447" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ447" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS447" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D196_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS447" t="inlineStr"/>
       <c r="AT447" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU447" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV447" t="inlineStr">
         <is>
@@ -61076,17 +61494,17 @@
       </c>
       <c r="AW447" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX447" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY447" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ447" t="inlineStr">
@@ -61096,17 +61514,17 @@
       </c>
       <c r="BA447" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB447" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC447" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -61133,17 +61551,17 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -61177,131 +61595,32 @@
         </is>
       </c>
       <c r="N448" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O448" t="n">
-        <v>32</v>
-      </c>
-      <c r="U448" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D196_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V448" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D196_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W448" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X448" t="inlineStr">
-        <is>
-          <t>West Nile Virus Infection</t>
-        </is>
-      </c>
-      <c r="Y448" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z448" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="R448" t="n">
+        <v>0</v>
       </c>
       <c r="AA448" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB448" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC448" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD448" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE448" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF448" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG448" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH448" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI448" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ448" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK448" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM448" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN448" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO448" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP448" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ448" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS448" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D196_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS448" t="inlineStr"/>
       <c r="AT448" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU448" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV448" t="inlineStr">
         <is>
@@ -61310,17 +61629,17 @@
       </c>
       <c r="AW448" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX448" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY448" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ448" t="inlineStr">
@@ -61330,17 +61649,17 @@
       </c>
       <c r="BA448" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB448" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC448" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -61372,12 +61691,12 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -61402,25 +61721,22 @@
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t>2004-02-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>2004-02</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N449" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O449" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q449" t="n">
         <v>0</v>
       </c>
       <c r="R449" t="n">
-        <v>0.01496507376259916</v>
+        <v>0</v>
       </c>
       <c r="AA449" t="inlineStr">
         <is>
@@ -61448,12 +61764,12 @@
       </c>
       <c r="AW449" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX449" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY449" t="inlineStr">
@@ -61468,12 +61784,12 @@
       </c>
       <c r="BA449" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB449" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC449" t="inlineStr">
@@ -61510,12 +61826,12 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -61540,12 +61856,12 @@
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>2004-02-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>2004-02</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N450" t="n">
@@ -61583,7 +61899,7 @@
       </c>
       <c r="AW450" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX450" t="inlineStr">
@@ -61603,7 +61919,7 @@
       </c>
       <c r="BA450" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB450" t="inlineStr">
@@ -61645,12 +61961,12 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -61675,41 +61991,65 @@
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>2004-02-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>2004-02</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N451" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O451" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="R451" t="n">
-        <v>0</v>
+        <v>0.09958709478847508</v>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D196_ANNUAL</t>
+        </is>
       </c>
       <c r="AA451" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO451" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP451" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS451" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ451" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS451" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D196_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT451" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU451" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV451" t="inlineStr">
         <is>
@@ -61718,17 +62058,17 @@
       </c>
       <c r="AW451" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX451" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY451" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ451" t="inlineStr">
@@ -61738,17 +62078,17 @@
       </c>
       <c r="BA451" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB451" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC451" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -61775,17 +62115,17 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -61810,41 +62150,140 @@
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>2004-02-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>2004-02</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N452" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O452" t="n">
-        <v>0</v>
-      </c>
-      <c r="R452" t="n">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D196_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V452" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D196_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W452" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X452" t="inlineStr">
+        <is>
+          <t>West Nile Virus Infection</t>
+        </is>
+      </c>
+      <c r="Y452" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z452" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
       </c>
       <c r="AA452" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB452" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC452" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD452" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE452" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF452" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG452" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH452" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI452" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ452" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK452" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM452" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN452" t="b">
+        <v>1</v>
       </c>
       <c r="AO452" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP452" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS452" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ452" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS452" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D196_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT452" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU452" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV452" t="inlineStr">
         <is>
@@ -61853,17 +62292,17 @@
       </c>
       <c r="AW452" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX452" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY452" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ452" t="inlineStr">
@@ -61873,17 +62312,17 @@
       </c>
       <c r="BA452" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB452" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC452" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -61915,12 +62354,12 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -61952,6 +62391,18 @@
         <is>
           <t>2004-02</t>
         </is>
+      </c>
+      <c r="N453" t="n">
+        <v>3</v>
+      </c>
+      <c r="O453" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q453" t="n">
+        <v>0</v>
+      </c>
+      <c r="R453" t="n">
+        <v>0.01496507376259916</v>
       </c>
       <c r="AA453" t="inlineStr">
         <is>
@@ -61979,12 +62430,12 @@
       </c>
       <c r="AW453" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX453" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY453" t="inlineStr">
@@ -61999,12 +62450,12 @@
       </c>
       <c r="BA453" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB453" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC453" t="inlineStr">
@@ -62041,12 +62492,12 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -62114,7 +62565,7 @@
       </c>
       <c r="AW454" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX454" t="inlineStr">
@@ -62134,7 +62585,7 @@
       </c>
       <c r="BA454" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB454" t="inlineStr">
@@ -62176,12 +62627,12 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -62249,7 +62700,7 @@
       </c>
       <c r="AW455" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX455" t="inlineStr">
@@ -62269,7 +62720,7 @@
       </c>
       <c r="BA455" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB455" t="inlineStr">
@@ -62311,12 +62762,12 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -62384,7 +62835,7 @@
       </c>
       <c r="AW456" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX456" t="inlineStr">
@@ -62404,7 +62855,7 @@
       </c>
       <c r="BA456" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB456" t="inlineStr">
@@ -62446,12 +62897,12 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -62483,15 +62934,6 @@
         <is>
           <t>2004-02</t>
         </is>
-      </c>
-      <c r="N457" t="n">
-        <v>0</v>
-      </c>
-      <c r="O457" t="n">
-        <v>0</v>
-      </c>
-      <c r="R457" t="n">
-        <v>0</v>
       </c>
       <c r="AA457" t="inlineStr">
         <is>
@@ -62519,7 +62961,7 @@
       </c>
       <c r="AW457" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX457" t="inlineStr">
@@ -62539,7 +62981,7 @@
       </c>
       <c r="BA457" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB457" t="inlineStr">
@@ -62581,12 +63023,12 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -62611,21 +63053,18 @@
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2004-02-01</t>
         </is>
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>2004-03</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="N458" t="n">
         <v>0</v>
       </c>
       <c r="O458" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q458" t="n">
         <v>0</v>
       </c>
       <c r="R458" t="n">
@@ -62657,12 +63096,12 @@
       </c>
       <c r="AW458" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX458" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY458" t="inlineStr">
@@ -62677,12 +63116,12 @@
       </c>
       <c r="BA458" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB458" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC458" t="inlineStr">
@@ -62719,12 +63158,12 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -62749,12 +63188,12 @@
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2004-02-01</t>
         </is>
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>2004-03</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="N459" t="n">
@@ -62792,7 +63231,7 @@
       </c>
       <c r="AW459" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX459" t="inlineStr">
@@ -62812,7 +63251,7 @@
       </c>
       <c r="BA459" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB459" t="inlineStr">
@@ -62854,12 +63293,12 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -62884,12 +63323,12 @@
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2004-02-01</t>
         </is>
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>2004-03</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="N460" t="n">
@@ -62927,7 +63366,7 @@
       </c>
       <c r="AW460" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX460" t="inlineStr">
@@ -62947,7 +63386,7 @@
       </c>
       <c r="BA460" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB460" t="inlineStr">
@@ -62989,12 +63428,12 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
@@ -63019,12 +63458,12 @@
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2004-02-01</t>
         </is>
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>2004-03</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="N461" t="n">
@@ -63062,7 +63501,7 @@
       </c>
       <c r="AW461" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX461" t="inlineStr">
@@ -63082,7 +63521,7 @@
       </c>
       <c r="BA461" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB461" t="inlineStr">
@@ -63124,12 +63563,12 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
@@ -63166,6 +63605,9 @@
         <v>0</v>
       </c>
       <c r="O462" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q462" t="n">
         <v>0</v>
       </c>
       <c r="R462" t="n">
@@ -63197,12 +63639,12 @@
       </c>
       <c r="AW462" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX462" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY462" t="inlineStr">
@@ -63217,12 +63659,12 @@
       </c>
       <c r="BA462" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB462" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC462" t="inlineStr">
@@ -63259,12 +63701,12 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
@@ -63332,7 +63774,7 @@
       </c>
       <c r="AW463" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX463" t="inlineStr">
@@ -63352,7 +63794,7 @@
       </c>
       <c r="BA463" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB463" t="inlineStr">
@@ -63394,12 +63836,12 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
@@ -63467,7 +63909,7 @@
       </c>
       <c r="AW464" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX464" t="inlineStr">
@@ -63487,7 +63929,7 @@
       </c>
       <c r="BA464" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB464" t="inlineStr">
@@ -63529,12 +63971,12 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -63602,7 +64044,7 @@
       </c>
       <c r="AW465" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX465" t="inlineStr">
@@ -63622,7 +64064,7 @@
       </c>
       <c r="BA465" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB465" t="inlineStr">
@@ -63664,12 +64106,12 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
@@ -63737,7 +64179,7 @@
       </c>
       <c r="AW466" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX466" t="inlineStr">
@@ -63757,7 +64199,7 @@
       </c>
       <c r="BA466" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB466" t="inlineStr">
@@ -63799,12 +64241,12 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
@@ -63829,21 +64271,18 @@
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>2004-04-01</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="N467" t="n">
         <v>0</v>
       </c>
       <c r="O467" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q467" t="n">
         <v>0</v>
       </c>
       <c r="R467" t="n">
@@ -63875,12 +64314,12 @@
       </c>
       <c r="AW467" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX467" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY467" t="inlineStr">
@@ -63895,12 +64334,12 @@
       </c>
       <c r="BA467" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB467" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC467" t="inlineStr">
@@ -63937,12 +64376,12 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -63967,12 +64406,12 @@
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>2004-04-01</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="N468" t="n">
@@ -64010,7 +64449,7 @@
       </c>
       <c r="AW468" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX468" t="inlineStr">
@@ -64030,7 +64469,7 @@
       </c>
       <c r="BA468" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB468" t="inlineStr">
@@ -64072,12 +64511,12 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -64102,12 +64541,12 @@
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>2004-04-01</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="N469" t="n">
@@ -64145,7 +64584,7 @@
       </c>
       <c r="AW469" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX469" t="inlineStr">
@@ -64165,7 +64604,7 @@
       </c>
       <c r="BA469" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB469" t="inlineStr">
@@ -64207,12 +64646,12 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -64237,12 +64676,12 @@
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>2004-04-01</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="N470" t="n">
@@ -64280,7 +64719,7 @@
       </c>
       <c r="AW470" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX470" t="inlineStr">
@@ -64300,7 +64739,7 @@
       </c>
       <c r="BA470" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB470" t="inlineStr">
@@ -64342,12 +64781,12 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -64384,6 +64823,9 @@
         <v>0</v>
       </c>
       <c r="O471" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q471" t="n">
         <v>0</v>
       </c>
       <c r="R471" t="n">
@@ -64415,12 +64857,12 @@
       </c>
       <c r="AW471" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX471" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY471" t="inlineStr">
@@ -64435,12 +64877,12 @@
       </c>
       <c r="BA471" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB471" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC471" t="inlineStr">
@@ -64477,12 +64919,12 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -64550,7 +64992,7 @@
       </c>
       <c r="AW472" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX472" t="inlineStr">
@@ -64570,7 +65012,7 @@
       </c>
       <c r="BA472" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB472" t="inlineStr">
@@ -64612,12 +65054,12 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -64685,7 +65127,7 @@
       </c>
       <c r="AW473" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX473" t="inlineStr">
@@ -64705,7 +65147,7 @@
       </c>
       <c r="BA473" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB473" t="inlineStr">
@@ -64747,12 +65189,12 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -64820,7 +65262,7 @@
       </c>
       <c r="AW474" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX474" t="inlineStr">
@@ -64840,7 +65282,7 @@
       </c>
       <c r="BA474" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB474" t="inlineStr">
@@ -64882,12 +65324,12 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -64955,7 +65397,7 @@
       </c>
       <c r="AW475" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX475" t="inlineStr">
@@ -64975,7 +65417,7 @@
       </c>
       <c r="BA475" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB475" t="inlineStr">
@@ -65017,12 +65459,12 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -65047,21 +65489,18 @@
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>2004-05-01</t>
+          <t>2004-04-01</t>
         </is>
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="N476" t="n">
         <v>0</v>
       </c>
       <c r="O476" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q476" t="n">
         <v>0</v>
       </c>
       <c r="R476" t="n">
@@ -65093,12 +65532,12 @@
       </c>
       <c r="AW476" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX476" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY476" t="inlineStr">
@@ -65113,12 +65552,12 @@
       </c>
       <c r="BA476" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB476" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC476" t="inlineStr">
@@ -65155,12 +65594,12 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -65185,12 +65624,12 @@
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>2004-05-01</t>
+          <t>2004-04-01</t>
         </is>
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="N477" t="n">
@@ -65228,7 +65667,7 @@
       </c>
       <c r="AW477" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX477" t="inlineStr">
@@ -65248,7 +65687,7 @@
       </c>
       <c r="BA477" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB477" t="inlineStr">
@@ -65290,12 +65729,12 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -65320,12 +65759,12 @@
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t>2004-05-01</t>
+          <t>2004-04-01</t>
         </is>
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="N478" t="n">
@@ -65363,7 +65802,7 @@
       </c>
       <c r="AW478" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX478" t="inlineStr">
@@ -65383,7 +65822,7 @@
       </c>
       <c r="BA478" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB478" t="inlineStr">
@@ -65425,12 +65864,12 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -65455,12 +65894,12 @@
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t>2004-05-01</t>
+          <t>2004-04-01</t>
         </is>
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="N479" t="n">
@@ -65498,7 +65937,7 @@
       </c>
       <c r="AW479" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX479" t="inlineStr">
@@ -65518,7 +65957,7 @@
       </c>
       <c r="BA479" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB479" t="inlineStr">
@@ -65560,12 +65999,12 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -65602,6 +66041,9 @@
         <v>0</v>
       </c>
       <c r="O480" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q480" t="n">
         <v>0</v>
       </c>
       <c r="R480" t="n">
@@ -65633,12 +66075,12 @@
       </c>
       <c r="AW480" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX480" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY480" t="inlineStr">
@@ -65653,12 +66095,12 @@
       </c>
       <c r="BA480" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB480" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC480" t="inlineStr">
@@ -65695,12 +66137,12 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -65768,7 +66210,7 @@
       </c>
       <c r="AW481" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX481" t="inlineStr">
@@ -65788,7 +66230,7 @@
       </c>
       <c r="BA481" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB481" t="inlineStr">
@@ -65830,12 +66272,12 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -65903,7 +66345,7 @@
       </c>
       <c r="AW482" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX482" t="inlineStr">
@@ -65923,7 +66365,7 @@
       </c>
       <c r="BA482" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB482" t="inlineStr">
@@ -65965,12 +66407,12 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
@@ -66038,7 +66480,7 @@
       </c>
       <c r="AW483" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX483" t="inlineStr">
@@ -66058,7 +66500,7 @@
       </c>
       <c r="BA483" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB483" t="inlineStr">
@@ -66100,12 +66542,12 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -66173,7 +66615,7 @@
       </c>
       <c r="AW484" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX484" t="inlineStr">
@@ -66193,7 +66635,7 @@
       </c>
       <c r="BA484" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB484" t="inlineStr">
@@ -66235,12 +66677,12 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -66265,21 +66707,18 @@
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N485" t="n">
         <v>0</v>
       </c>
       <c r="O485" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q485" t="n">
         <v>0</v>
       </c>
       <c r="R485" t="n">
@@ -66311,12 +66750,12 @@
       </c>
       <c r="AW485" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX485" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY485" t="inlineStr">
@@ -66331,12 +66770,12 @@
       </c>
       <c r="BA485" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB485" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC485" t="inlineStr">
@@ -66373,12 +66812,12 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -66403,12 +66842,12 @@
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N486" t="n">
@@ -66446,7 +66885,7 @@
       </c>
       <c r="AW486" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX486" t="inlineStr">
@@ -66466,7 +66905,7 @@
       </c>
       <c r="BA486" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB486" t="inlineStr">
@@ -66508,12 +66947,12 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -66538,12 +66977,12 @@
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N487" t="n">
@@ -66581,7 +67020,7 @@
       </c>
       <c r="AW487" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX487" t="inlineStr">
@@ -66601,7 +67040,7 @@
       </c>
       <c r="BA487" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB487" t="inlineStr">
@@ -66643,12 +67082,12 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -66673,12 +67112,12 @@
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N488" t="n">
@@ -66716,7 +67155,7 @@
       </c>
       <c r="AW488" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX488" t="inlineStr">
@@ -66736,7 +67175,7 @@
       </c>
       <c r="BA488" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB488" t="inlineStr">
@@ -66778,12 +67217,12 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -66820,6 +67259,9 @@
         <v>0</v>
       </c>
       <c r="O489" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q489" t="n">
         <v>0</v>
       </c>
       <c r="R489" t="n">
@@ -66851,12 +67293,12 @@
       </c>
       <c r="AW489" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX489" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY489" t="inlineStr">
@@ -66871,12 +67313,12 @@
       </c>
       <c r="BA489" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB489" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC489" t="inlineStr">
@@ -66913,12 +67355,12 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
@@ -66986,7 +67428,7 @@
       </c>
       <c r="AW490" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX490" t="inlineStr">
@@ -67006,7 +67448,7 @@
       </c>
       <c r="BA490" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB490" t="inlineStr">
@@ -67048,12 +67490,12 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -67121,7 +67563,7 @@
       </c>
       <c r="AW491" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX491" t="inlineStr">
@@ -67141,7 +67583,7 @@
       </c>
       <c r="BA491" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB491" t="inlineStr">
@@ -67183,12 +67625,12 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -67256,7 +67698,7 @@
       </c>
       <c r="AW492" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX492" t="inlineStr">
@@ -67276,7 +67718,7 @@
       </c>
       <c r="BA492" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB492" t="inlineStr">
@@ -67318,12 +67760,12 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -67391,7 +67833,7 @@
       </c>
       <c r="AW493" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX493" t="inlineStr">
@@ -67411,7 +67853,7 @@
       </c>
       <c r="BA493" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB493" t="inlineStr">
@@ -67453,12 +67895,12 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -67483,21 +67925,18 @@
       </c>
       <c r="L494" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N494" t="n">
         <v>0</v>
       </c>
       <c r="O494" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q494" t="n">
         <v>0</v>
       </c>
       <c r="R494" t="n">
@@ -67529,12 +67968,12 @@
       </c>
       <c r="AW494" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX494" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY494" t="inlineStr">
@@ -67549,12 +67988,12 @@
       </c>
       <c r="BA494" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB494" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC494" t="inlineStr">
@@ -67591,12 +68030,12 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -67621,12 +68060,12 @@
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N495" t="n">
@@ -67664,7 +68103,7 @@
       </c>
       <c r="AW495" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX495" t="inlineStr">
@@ -67684,7 +68123,7 @@
       </c>
       <c r="BA495" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB495" t="inlineStr">
@@ -67726,12 +68165,12 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -67756,12 +68195,12 @@
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N496" t="n">
@@ -67799,7 +68238,7 @@
       </c>
       <c r="AW496" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX496" t="inlineStr">
@@ -67819,7 +68258,7 @@
       </c>
       <c r="BA496" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB496" t="inlineStr">
@@ -67861,12 +68300,12 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -67891,12 +68330,12 @@
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N497" t="n">
@@ -67934,7 +68373,7 @@
       </c>
       <c r="AW497" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX497" t="inlineStr">
@@ -67954,7 +68393,7 @@
       </c>
       <c r="BA497" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB497" t="inlineStr">
@@ -67996,12 +68435,12 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -68038,6 +68477,9 @@
         <v>0</v>
       </c>
       <c r="O498" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q498" t="n">
         <v>0</v>
       </c>
       <c r="R498" t="n">
@@ -68069,12 +68511,12 @@
       </c>
       <c r="AW498" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX498" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY498" t="inlineStr">
@@ -68089,12 +68531,12 @@
       </c>
       <c r="BA498" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB498" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC498" t="inlineStr">
@@ -68131,12 +68573,12 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -68204,7 +68646,7 @@
       </c>
       <c r="AW499" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX499" t="inlineStr">
@@ -68224,7 +68666,7 @@
       </c>
       <c r="BA499" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB499" t="inlineStr">
@@ -68266,12 +68708,12 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -68339,7 +68781,7 @@
       </c>
       <c r="AW500" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX500" t="inlineStr">
@@ -68359,7 +68801,7 @@
       </c>
       <c r="BA500" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB500" t="inlineStr">
@@ -68401,12 +68843,12 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -68474,7 +68916,7 @@
       </c>
       <c r="AW501" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX501" t="inlineStr">
@@ -68494,7 +68936,7 @@
       </c>
       <c r="BA501" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB501" t="inlineStr">
@@ -68536,12 +68978,12 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -68609,7 +69051,7 @@
       </c>
       <c r="AW502" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX502" t="inlineStr">
@@ -68629,7 +69071,7 @@
       </c>
       <c r="BA502" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB502" t="inlineStr">
@@ -68671,12 +69113,12 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
@@ -68701,21 +69143,18 @@
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="M503" t="inlineStr">
         <is>
-          <t>2004-08</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="N503" t="n">
         <v>0</v>
       </c>
       <c r="O503" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q503" t="n">
         <v>0</v>
       </c>
       <c r="R503" t="n">
@@ -68747,12 +69186,12 @@
       </c>
       <c r="AW503" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX503" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY503" t="inlineStr">
@@ -68767,12 +69206,12 @@
       </c>
       <c r="BA503" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB503" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC503" t="inlineStr">
@@ -68809,12 +69248,12 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -68839,12 +69278,12 @@
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="M504" t="inlineStr">
         <is>
-          <t>2004-08</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="N504" t="n">
@@ -68882,7 +69321,7 @@
       </c>
       <c r="AW504" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX504" t="inlineStr">
@@ -68902,7 +69341,7 @@
       </c>
       <c r="BA504" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB504" t="inlineStr">
@@ -68944,12 +69383,12 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -68974,12 +69413,12 @@
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="M505" t="inlineStr">
         <is>
-          <t>2004-08</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="N505" t="n">
@@ -69017,7 +69456,7 @@
       </c>
       <c r="AW505" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX505" t="inlineStr">
@@ -69037,7 +69476,7 @@
       </c>
       <c r="BA505" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB505" t="inlineStr">
@@ -69079,12 +69518,12 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
@@ -69109,12 +69548,12 @@
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="M506" t="inlineStr">
         <is>
-          <t>2004-08</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="N506" t="n">
@@ -69152,7 +69591,7 @@
       </c>
       <c r="AW506" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX506" t="inlineStr">
@@ -69172,7 +69611,7 @@
       </c>
       <c r="BA506" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB506" t="inlineStr">
@@ -69214,12 +69653,12 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -69256,6 +69695,9 @@
         <v>0</v>
       </c>
       <c r="O507" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q507" t="n">
         <v>0</v>
       </c>
       <c r="R507" t="n">
@@ -69287,12 +69729,12 @@
       </c>
       <c r="AW507" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX507" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY507" t="inlineStr">
@@ -69307,12 +69749,12 @@
       </c>
       <c r="BA507" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB507" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC507" t="inlineStr">
@@ -69349,12 +69791,12 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
@@ -69422,7 +69864,7 @@
       </c>
       <c r="AW508" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX508" t="inlineStr">
@@ -69442,7 +69884,7 @@
       </c>
       <c r="BA508" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB508" t="inlineStr">
@@ -69484,12 +69926,12 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
@@ -69557,7 +69999,7 @@
       </c>
       <c r="AW509" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX509" t="inlineStr">
@@ -69577,7 +70019,7 @@
       </c>
       <c r="BA509" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB509" t="inlineStr">
@@ -69619,12 +70061,12 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -69692,7 +70134,7 @@
       </c>
       <c r="AW510" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX510" t="inlineStr">
@@ -69712,7 +70154,7 @@
       </c>
       <c r="BA510" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB510" t="inlineStr">
@@ -69754,12 +70196,12 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -69827,7 +70269,7 @@
       </c>
       <c r="AW511" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX511" t="inlineStr">
@@ -69847,7 +70289,7 @@
       </c>
       <c r="BA511" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB511" t="inlineStr">
@@ -69889,12 +70331,12 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -69919,21 +70361,18 @@
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t>2004-09-01</t>
+          <t>2004-08-01</t>
         </is>
       </c>
       <c r="M512" t="inlineStr">
         <is>
-          <t>2004-09</t>
+          <t>2004-08</t>
         </is>
       </c>
       <c r="N512" t="n">
         <v>0</v>
       </c>
       <c r="O512" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q512" t="n">
         <v>0</v>
       </c>
       <c r="R512" t="n">
@@ -69965,12 +70404,12 @@
       </c>
       <c r="AW512" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX512" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY512" t="inlineStr">
@@ -69985,12 +70424,12 @@
       </c>
       <c r="BA512" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB512" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC512" t="inlineStr">
@@ -70027,12 +70466,12 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -70057,12 +70496,12 @@
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>2004-09-01</t>
+          <t>2004-08-01</t>
         </is>
       </c>
       <c r="M513" t="inlineStr">
         <is>
-          <t>2004-09</t>
+          <t>2004-08</t>
         </is>
       </c>
       <c r="N513" t="n">
@@ -70100,7 +70539,7 @@
       </c>
       <c r="AW513" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX513" t="inlineStr">
@@ -70120,7 +70559,7 @@
       </c>
       <c r="BA513" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB513" t="inlineStr">
@@ -70162,12 +70601,12 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -70192,12 +70631,12 @@
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t>2004-09-01</t>
+          <t>2004-08-01</t>
         </is>
       </c>
       <c r="M514" t="inlineStr">
         <is>
-          <t>2004-09</t>
+          <t>2004-08</t>
         </is>
       </c>
       <c r="N514" t="n">
@@ -70235,7 +70674,7 @@
       </c>
       <c r="AW514" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX514" t="inlineStr">
@@ -70255,7 +70694,7 @@
       </c>
       <c r="BA514" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB514" t="inlineStr">
@@ -70297,12 +70736,12 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
@@ -70327,12 +70766,12 @@
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>2004-09-01</t>
+          <t>2004-08-01</t>
         </is>
       </c>
       <c r="M515" t="inlineStr">
         <is>
-          <t>2004-09</t>
+          <t>2004-08</t>
         </is>
       </c>
       <c r="N515" t="n">
@@ -70370,7 +70809,7 @@
       </c>
       <c r="AW515" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX515" t="inlineStr">
@@ -70390,7 +70829,7 @@
       </c>
       <c r="BA515" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB515" t="inlineStr">
@@ -70432,12 +70871,12 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
@@ -70474,6 +70913,9 @@
         <v>0</v>
       </c>
       <c r="O516" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q516" t="n">
         <v>0</v>
       </c>
       <c r="R516" t="n">
@@ -70505,12 +70947,12 @@
       </c>
       <c r="AW516" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX516" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY516" t="inlineStr">
@@ -70525,12 +70967,12 @@
       </c>
       <c r="BA516" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB516" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC516" t="inlineStr">
@@ -70567,12 +71009,12 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -70640,7 +71082,7 @@
       </c>
       <c r="AW517" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX517" t="inlineStr">
@@ -70660,7 +71102,7 @@
       </c>
       <c r="BA517" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB517" t="inlineStr">
@@ -70702,12 +71144,12 @@
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
@@ -70775,7 +71217,7 @@
       </c>
       <c r="AW518" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX518" t="inlineStr">
@@ -70795,7 +71237,7 @@
       </c>
       <c r="BA518" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB518" t="inlineStr">
@@ -70837,12 +71279,12 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -70910,7 +71352,7 @@
       </c>
       <c r="AW519" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX519" t="inlineStr">
@@ -70930,7 +71372,7 @@
       </c>
       <c r="BA519" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB519" t="inlineStr">
@@ -70972,12 +71414,12 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
@@ -71045,7 +71487,7 @@
       </c>
       <c r="AW520" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX520" t="inlineStr">
@@ -71065,7 +71507,7 @@
       </c>
       <c r="BA520" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB520" t="inlineStr">
@@ -71107,12 +71549,12 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
@@ -71137,25 +71579,22 @@
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t>2004-10-01</t>
+          <t>2004-09-01</t>
         </is>
       </c>
       <c r="M521" t="inlineStr">
         <is>
-          <t>2004-10</t>
+          <t>2004-09</t>
         </is>
       </c>
       <c r="N521" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O521" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q521" t="n">
         <v>0</v>
       </c>
       <c r="R521" t="n">
-        <v>0.004988357920866386</v>
+        <v>0</v>
       </c>
       <c r="AA521" t="inlineStr">
         <is>
@@ -71183,12 +71622,12 @@
       </c>
       <c r="AW521" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX521" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY521" t="inlineStr">
@@ -71203,12 +71642,12 @@
       </c>
       <c r="BA521" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB521" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC521" t="inlineStr">
@@ -71245,12 +71684,12 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
@@ -71275,12 +71714,12 @@
       </c>
       <c r="L522" t="inlineStr">
         <is>
-          <t>2004-10-01</t>
+          <t>2004-09-01</t>
         </is>
       </c>
       <c r="M522" t="inlineStr">
         <is>
-          <t>2004-10</t>
+          <t>2004-09</t>
         </is>
       </c>
       <c r="N522" t="n">
@@ -71318,7 +71757,7 @@
       </c>
       <c r="AW522" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX522" t="inlineStr">
@@ -71338,7 +71777,7 @@
       </c>
       <c r="BA522" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB522" t="inlineStr">
@@ -71380,12 +71819,12 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -71410,12 +71849,12 @@
       </c>
       <c r="L523" t="inlineStr">
         <is>
-          <t>2004-10-01</t>
+          <t>2004-09-01</t>
         </is>
       </c>
       <c r="M523" t="inlineStr">
         <is>
-          <t>2004-10</t>
+          <t>2004-09</t>
         </is>
       </c>
       <c r="N523" t="n">
@@ -71453,7 +71892,7 @@
       </c>
       <c r="AW523" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX523" t="inlineStr">
@@ -71473,7 +71912,7 @@
       </c>
       <c r="BA523" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB523" t="inlineStr">
@@ -71515,12 +71954,12 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -71545,12 +71984,12 @@
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t>2004-10-01</t>
+          <t>2004-09-01</t>
         </is>
       </c>
       <c r="M524" t="inlineStr">
         <is>
-          <t>2004-10</t>
+          <t>2004-09</t>
         </is>
       </c>
       <c r="N524" t="n">
@@ -71588,7 +72027,7 @@
       </c>
       <c r="AW524" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX524" t="inlineStr">
@@ -71608,7 +72047,7 @@
       </c>
       <c r="BA524" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB524" t="inlineStr">
@@ -71650,12 +72089,12 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -71689,13 +72128,16 @@
         </is>
       </c>
       <c r="N525" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O525" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q525" t="n">
         <v>0</v>
       </c>
       <c r="R525" t="n">
-        <v>0</v>
+        <v>0.004988357920866386</v>
       </c>
       <c r="AA525" t="inlineStr">
         <is>
@@ -71723,12 +72165,12 @@
       </c>
       <c r="AW525" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX525" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY525" t="inlineStr">
@@ -71743,12 +72185,12 @@
       </c>
       <c r="BA525" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB525" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC525" t="inlineStr">
@@ -71785,12 +72227,12 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
@@ -71858,7 +72300,7 @@
       </c>
       <c r="AW526" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX526" t="inlineStr">
@@ -71878,7 +72320,7 @@
       </c>
       <c r="BA526" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB526" t="inlineStr">
@@ -71920,12 +72362,12 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -71993,7 +72435,7 @@
       </c>
       <c r="AW527" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX527" t="inlineStr">
@@ -72013,7 +72455,7 @@
       </c>
       <c r="BA527" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB527" t="inlineStr">
@@ -72055,12 +72497,12 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -72092,6 +72534,15 @@
         <is>
           <t>2004-10</t>
         </is>
+      </c>
+      <c r="N528" t="n">
+        <v>0</v>
+      </c>
+      <c r="O528" t="n">
+        <v>0</v>
+      </c>
+      <c r="R528" t="n">
+        <v>0</v>
       </c>
       <c r="AA528" t="inlineStr">
         <is>
@@ -72119,7 +72570,7 @@
       </c>
       <c r="AW528" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX528" t="inlineStr">
@@ -72139,7 +72590,7 @@
       </c>
       <c r="BA528" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB528" t="inlineStr">
@@ -72181,12 +72632,12 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -72254,7 +72705,7 @@
       </c>
       <c r="AW529" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX529" t="inlineStr">
@@ -72274,7 +72725,7 @@
       </c>
       <c r="BA529" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB529" t="inlineStr">
@@ -72316,12 +72767,12 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -72346,21 +72797,18 @@
       </c>
       <c r="L530" t="inlineStr">
         <is>
-          <t>2004-11-01</t>
+          <t>2004-10-01</t>
         </is>
       </c>
       <c r="M530" t="inlineStr">
         <is>
-          <t>2004-11</t>
+          <t>2004-10</t>
         </is>
       </c>
       <c r="N530" t="n">
         <v>0</v>
       </c>
       <c r="O530" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q530" t="n">
         <v>0</v>
       </c>
       <c r="R530" t="n">
@@ -72392,12 +72840,12 @@
       </c>
       <c r="AW530" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX530" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY530" t="inlineStr">
@@ -72412,12 +72860,12 @@
       </c>
       <c r="BA530" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB530" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC530" t="inlineStr">
@@ -72454,12 +72902,12 @@
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
@@ -72484,12 +72932,12 @@
       </c>
       <c r="L531" t="inlineStr">
         <is>
-          <t>2004-11-01</t>
+          <t>2004-10-01</t>
         </is>
       </c>
       <c r="M531" t="inlineStr">
         <is>
-          <t>2004-11</t>
+          <t>2004-10</t>
         </is>
       </c>
       <c r="N531" t="n">
@@ -72527,7 +72975,7 @@
       </c>
       <c r="AW531" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX531" t="inlineStr">
@@ -72547,7 +72995,7 @@
       </c>
       <c r="BA531" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB531" t="inlineStr">
@@ -72589,12 +73037,12 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
@@ -72619,22 +73067,13 @@
       </c>
       <c r="L532" t="inlineStr">
         <is>
-          <t>2004-11-01</t>
+          <t>2004-10-01</t>
         </is>
       </c>
       <c r="M532" t="inlineStr">
         <is>
-          <t>2004-11</t>
-        </is>
-      </c>
-      <c r="N532" t="n">
-        <v>0</v>
-      </c>
-      <c r="O532" t="n">
-        <v>0</v>
-      </c>
-      <c r="R532" t="n">
-        <v>0</v>
+          <t>2004-10</t>
+        </is>
       </c>
       <c r="AA532" t="inlineStr">
         <is>
@@ -72662,7 +73101,7 @@
       </c>
       <c r="AW532" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX532" t="inlineStr">
@@ -72682,7 +73121,7 @@
       </c>
       <c r="BA532" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB532" t="inlineStr">
@@ -72724,12 +73163,12 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
@@ -72754,12 +73193,12 @@
       </c>
       <c r="L533" t="inlineStr">
         <is>
-          <t>2004-11-01</t>
+          <t>2004-10-01</t>
         </is>
       </c>
       <c r="M533" t="inlineStr">
         <is>
-          <t>2004-11</t>
+          <t>2004-10</t>
         </is>
       </c>
       <c r="N533" t="n">
@@ -72797,7 +73236,7 @@
       </c>
       <c r="AW533" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX533" t="inlineStr">
@@ -72817,7 +73256,7 @@
       </c>
       <c r="BA533" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB533" t="inlineStr">
@@ -72859,12 +73298,12 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
@@ -72901,6 +73340,9 @@
         <v>0</v>
       </c>
       <c r="O534" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q534" t="n">
         <v>0</v>
       </c>
       <c r="R534" t="n">
@@ -72932,12 +73374,12 @@
       </c>
       <c r="AW534" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX534" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY534" t="inlineStr">
@@ -72952,12 +73394,12 @@
       </c>
       <c r="BA534" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB534" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC534" t="inlineStr">
@@ -72994,12 +73436,12 @@
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -73067,7 +73509,7 @@
       </c>
       <c r="AW535" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX535" t="inlineStr">
@@ -73087,7 +73529,7 @@
       </c>
       <c r="BA535" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB535" t="inlineStr">
@@ -73129,12 +73571,12 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
@@ -73202,7 +73644,7 @@
       </c>
       <c r="AW536" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX536" t="inlineStr">
@@ -73222,7 +73664,7 @@
       </c>
       <c r="BA536" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB536" t="inlineStr">
@@ -73264,12 +73706,12 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
@@ -73337,7 +73779,7 @@
       </c>
       <c r="AW537" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX537" t="inlineStr">
@@ -73357,7 +73799,7 @@
       </c>
       <c r="BA537" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB537" t="inlineStr">
@@ -73399,12 +73841,12 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
@@ -73472,7 +73914,7 @@
       </c>
       <c r="AW538" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX538" t="inlineStr">
@@ -73492,7 +73934,7 @@
       </c>
       <c r="BA538" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB538" t="inlineStr">
@@ -73534,12 +73976,12 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>DE-TH</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>Thüringen, Germany</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
@@ -73573,24 +74015,22 @@
         </is>
       </c>
       <c r="N539" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O539" t="n">
-        <v>1</v>
-      </c>
-      <c r="U539" t="inlineStr">
-        <is>
-          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="R539" t="n">
+        <v>0</v>
       </c>
       <c r="AA539" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO539" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP539" t="inlineStr">
@@ -73598,52 +74038,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS539" t="inlineStr">
-        <is>
-          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
-        </is>
-      </c>
+      <c r="AS539" t="inlineStr"/>
       <c r="AT539" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV539" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW539" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX539" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY539" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ539" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA539" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB539" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC539" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -73675,12 +74111,12 @@
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H540" t="inlineStr">
@@ -73705,25 +74141,22 @@
       </c>
       <c r="L540" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-11-01</t>
         </is>
       </c>
       <c r="M540" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2004-11</t>
         </is>
       </c>
       <c r="N540" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O540" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q540" t="n">
         <v>0</v>
       </c>
       <c r="R540" t="n">
-        <v>0.004988357920866386</v>
+        <v>0</v>
       </c>
       <c r="AA540" t="inlineStr">
         <is>
@@ -73751,12 +74184,12 @@
       </c>
       <c r="AW540" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX540" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY540" t="inlineStr">
@@ -73771,12 +74204,12 @@
       </c>
       <c r="BA540" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB540" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC540" t="inlineStr">
@@ -73813,12 +74246,12 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
@@ -73843,12 +74276,12 @@
       </c>
       <c r="L541" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-11-01</t>
         </is>
       </c>
       <c r="M541" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2004-11</t>
         </is>
       </c>
       <c r="N541" t="n">
@@ -73886,7 +74319,7 @@
       </c>
       <c r="AW541" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX541" t="inlineStr">
@@ -73906,7 +74339,7 @@
       </c>
       <c r="BA541" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB541" t="inlineStr">
@@ -73948,12 +74381,12 @@
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -73978,12 +74411,12 @@
       </c>
       <c r="L542" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-11-01</t>
         </is>
       </c>
       <c r="M542" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2004-11</t>
         </is>
       </c>
       <c r="N542" t="n">
@@ -74021,7 +74454,7 @@
       </c>
       <c r="AW542" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX542" t="inlineStr">
@@ -74041,7 +74474,7 @@
       </c>
       <c r="BA542" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB542" t="inlineStr">
@@ -74078,17 +74511,17 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
@@ -74113,80 +74546,187 @@
       </c>
       <c r="L543" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-11-01</t>
         </is>
       </c>
       <c r="M543" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2004-11</t>
         </is>
       </c>
       <c r="N543" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O543" t="n">
-        <v>0</v>
-      </c>
-      <c r="R543" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P543" t="n">
+        <v>1</v>
+      </c>
+      <c r="U543" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="V543" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="W543" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X543" t="inlineStr">
+        <is>
+          <t>__source_native__</t>
+        </is>
+      </c>
+      <c r="Y543" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z543" t="inlineStr">
+        <is>
+          <t>national_ifsG_notification_registry</t>
+        </is>
       </c>
       <c r="AA543" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB543" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC543" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD543" t="inlineStr">
+        <is>
+          <t>sha256:ffcb24f78ecc3d9ae732caf86a9d5bdb915c979773cdb4a208a655097464cc61</t>
+        </is>
+      </c>
+      <c r="AE543" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF543" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG543" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH543" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI543" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ543" t="inlineStr">
+        <is>
+          <t>DE_RKI_SURVSTAT_source_native</t>
+        </is>
+      </c>
+      <c r="AK543" t="inlineStr">
+        <is>
+          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
+        </is>
+      </c>
+      <c r="AM543" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN543" t="b">
+        <v>0</v>
       </c>
       <c r="AO543" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP543" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS543" t="inlineStr"/>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ543" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR543" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS543" t="inlineStr">
+        <is>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
+        </is>
+      </c>
       <c r="AT543" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="AU543" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV543" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW543" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX543" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY543" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ543" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA543" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB543" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC543" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -74218,12 +74758,12 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>DE-TH</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Thüringen, Germany</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
@@ -74248,71 +74788,101 @@
       </c>
       <c r="L544" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-11-01</t>
         </is>
       </c>
       <c r="M544" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2004-11</t>
+        </is>
+      </c>
+      <c r="N544" t="n">
+        <v>1</v>
+      </c>
+      <c r="O544" t="n">
+        <v>1</v>
+      </c>
+      <c r="S544" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U544" t="inlineStr">
+        <is>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
         </is>
       </c>
       <c r="AA544" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO544" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP544" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS544" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ544" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS544" t="inlineStr">
+        <is>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
+        </is>
+      </c>
       <c r="AT544" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU544" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV544" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW544" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX544" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY544" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ544" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA544" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB544" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC544" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -74339,17 +74909,17 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>DE-TH</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Thüringen, Germany</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
@@ -74374,80 +74944,179 @@
       </c>
       <c r="L545" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-11-01</t>
         </is>
       </c>
       <c r="M545" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2004-11</t>
         </is>
       </c>
       <c r="N545" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O545" t="n">
-        <v>0</v>
-      </c>
-      <c r="R545" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="U545" t="inlineStr">
+        <is>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
+        </is>
+      </c>
+      <c r="V545" t="inlineStr">
+        <is>
+          <t>west-nil-virus</t>
+        </is>
+      </c>
+      <c r="W545" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X545" t="inlineStr">
+        <is>
+          <t>West-Nil-Virus</t>
+        </is>
+      </c>
+      <c r="Y545" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z545" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
       </c>
       <c r="AA545" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB545" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC545" t="inlineStr">
+        <is>
+          <t>country:DE-TH:national</t>
+        </is>
+      </c>
+      <c r="AD545" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE545" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF545" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG545" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH545" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI545" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ545" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL545" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM545" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN545" t="b">
+        <v>1</v>
       </c>
       <c r="AO545" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP545" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS545" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ545" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS545" t="inlineStr">
+        <is>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
+        </is>
+      </c>
       <c r="AT545" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU545" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV545" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW545" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX545" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY545" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ545" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA545" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB545" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC545" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -74479,12 +75148,12 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -74518,13 +75187,16 @@
         </is>
       </c>
       <c r="N546" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O546" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q546" t="n">
         <v>0</v>
       </c>
       <c r="R546" t="n">
-        <v>0</v>
+        <v>0.004988357920866386</v>
       </c>
       <c r="AA546" t="inlineStr">
         <is>
@@ -74552,12 +75224,12 @@
       </c>
       <c r="AW546" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX546" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY546" t="inlineStr">
@@ -74572,12 +75244,12 @@
       </c>
       <c r="BA546" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB546" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC546" t="inlineStr">
@@ -74614,12 +75286,12 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -74687,7 +75359,7 @@
       </c>
       <c r="AW547" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX547" t="inlineStr">
@@ -74707,7 +75379,7 @@
       </c>
       <c r="BA547" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB547" t="inlineStr">
@@ -74749,12 +75421,12 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
@@ -74822,35 +75494,836 @@
       </c>
       <c r="AW548" t="inlineStr">
         <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX548" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY548" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ548" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA548" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB548" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC548" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>2004-12</t>
+        </is>
+      </c>
+      <c r="N549" t="n">
+        <v>0</v>
+      </c>
+      <c r="O549" t="n">
+        <v>0</v>
+      </c>
+      <c r="R549" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA549" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO549" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP549" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS549" t="inlineStr"/>
+      <c r="AT549" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV549" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW549" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX549" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY549" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ549" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA549" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB549" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC549" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>2004-12</t>
+        </is>
+      </c>
+      <c r="AA550" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO550" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP550" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS550" t="inlineStr"/>
+      <c r="AT550" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV550" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW550" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX550" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY550" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ550" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA550" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB550" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC550" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>2004-12</t>
+        </is>
+      </c>
+      <c r="N551" t="n">
+        <v>0</v>
+      </c>
+      <c r="O551" t="n">
+        <v>0</v>
+      </c>
+      <c r="R551" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA551" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO551" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP551" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS551" t="inlineStr"/>
+      <c r="AT551" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV551" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW551" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX551" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY551" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ551" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA551" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB551" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC551" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>2004-12</t>
+        </is>
+      </c>
+      <c r="N552" t="n">
+        <v>0</v>
+      </c>
+      <c r="O552" t="n">
+        <v>0</v>
+      </c>
+      <c r="R552" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA552" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO552" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP552" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS552" t="inlineStr"/>
+      <c r="AT552" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV552" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW552" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX552" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY552" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ552" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA552" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB552" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC552" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>2004-12</t>
+        </is>
+      </c>
+      <c r="N553" t="n">
+        <v>0</v>
+      </c>
+      <c r="O553" t="n">
+        <v>0</v>
+      </c>
+      <c r="R553" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA553" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO553" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP553" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS553" t="inlineStr"/>
+      <c r="AT553" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV553" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW553" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX553" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY553" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ553" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA553" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB553" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC553" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>2004-12</t>
+        </is>
+      </c>
+      <c r="N554" t="n">
+        <v>0</v>
+      </c>
+      <c r="O554" t="n">
+        <v>0</v>
+      </c>
+      <c r="R554" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA554" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO554" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP554" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS554" t="inlineStr"/>
+      <c r="AT554" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV554" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW554" t="inlineStr">
+        <is>
           <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
-      <c r="AX548" t="inlineStr">
-        <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
-        </is>
-      </c>
-      <c r="AY548" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ548" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="BA548" t="inlineStr">
+      <c r="AX554" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY554" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ554" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA554" t="inlineStr">
         <is>
           <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
-      <c r="BB548" t="inlineStr">
-        <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
-        </is>
-      </c>
-      <c r="BC548" t="inlineStr">
+      <c r="BB554" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC554" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -74982,7 +76455,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>547</v>
+        <v>553</v>
       </c>
     </row>
     <row r="11">
@@ -75002,7 +76475,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -75012,7 +76485,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
